--- a/PHOENIX_OMEGA_INVESTOR_DD.xlsx
+++ b/PHOENIX_OMEGA_INVESTOR_DD.xlsx
@@ -1586,9 +1586,9 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C26:D26"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
